--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -1181,10 +1181,7 @@
     <t>このシリーズの対象となる解剖学的部位。</t>
   </si>
   <si>
-    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1775,7 +1772,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="28.546875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="87.2265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -6415,11 +6412,9 @@
       <c r="X40" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Y40" s="2"/>
+      <c r="Z40" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6455,10 +6450,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6469,10 +6464,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6498,10 +6493,10 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>265</v>
@@ -6533,11 +6528,11 @@
         <v>284</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6554,7 +6549,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6572,10 +6567,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6586,10 +6581,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6612,13 +6607,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>265</v>
@@ -6671,7 +6666,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6689,10 +6684,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6703,10 +6698,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6732,13 +6727,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6788,7 +6783,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6809,7 +6804,7 @@
         <v>203</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6820,14 +6815,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6849,16 +6844,16 @@
         <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>265</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6907,7 +6902,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6922,13 +6917,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>229</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6939,10 +6934,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7054,10 +7049,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7171,10 +7166,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7290,10 +7285,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7319,16 +7314,16 @@
         <v>262</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>265</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7356,11 +7351,11 @@
         <v>266</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7377,7 +7372,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7409,10 +7404,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7435,13 +7430,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>265</v>
@@ -7494,7 +7489,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7512,24 +7507,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7555,10 +7550,10 @@
         <v>313</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7609,7 +7604,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7627,7 +7622,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7641,10 +7636,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7756,10 +7751,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7873,10 +7868,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7992,14 +7987,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8021,16 +8016,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8043,7 +8038,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8079,7 +8074,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8100,7 +8095,7 @@
         <v>337</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8111,14 +8106,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8140,13 +8135,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8175,11 +8170,11 @@
         <v>266</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8196,7 +8191,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8214,10 +8209,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8228,14 +8223,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8257,13 +8252,13 @@
         <v>241</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8313,7 +8308,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8331,10 +8326,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8345,10 +8340,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8374,13 +8369,13 @@
         <v>306</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8430,7 +8425,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8448,10 +8443,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
